--- a/dev/all-profiles.xlsx
+++ b/dev/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
